--- a/WorkBot/refactor-experimental/data/orders/Regional Distributors, Inc/Regional Distributors, Inc._Collegetown_20251114.xlsx
+++ b/WorkBot/refactor-experimental/data/orders/Regional Distributors, Inc/Regional Distributors, Inc._Collegetown_20251114.xlsx
@@ -454,20 +454,14 @@
           <t>Wrap - Hot Sandwich Cushion (14" x 16")</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>38.65</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>154.60</t>
-        </is>
+      <c r="C2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D2" t="n">
+        <v>38.65</v>
+      </c>
+      <c r="E2" t="n">
+        <v>154.6</v>
       </c>
     </row>
     <row r="3">
@@ -481,20 +475,14 @@
           <t>Lid - Hot Cup (12/16/20oz)</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>50.89</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>50.89</t>
-        </is>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>50.89</v>
+      </c>
+      <c r="E3" t="n">
+        <v>50.89</v>
       </c>
     </row>
     <row r="4">
@@ -508,20 +496,14 @@
           <t>Trash Bag (38x58)</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>36.14</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>36.14</t>
-        </is>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>36.14</v>
+      </c>
+      <c r="E4" t="n">
+        <v>36.14</v>
       </c>
     </row>
     <row r="5">
@@ -535,20 +517,14 @@
           <t>Wrap - Cold Sandwich (18" x 18")</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>102.85</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>102.85</t>
-        </is>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>102.85</v>
+      </c>
+      <c r="E5" t="n">
+        <v>102.85</v>
       </c>
     </row>
     <row r="6">
@@ -562,20 +538,14 @@
           <t>Towel Disp Folded</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>55.23</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>55.23</t>
-        </is>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>55.23</v>
+      </c>
+      <c r="E6" t="n">
+        <v>55.23</v>
       </c>
     </row>
     <row r="7">
@@ -589,20 +559,14 @@
           <t>Lid Cold Sip - 16/24oz</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>42.97</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>85.94</t>
-        </is>
+      <c r="C7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" t="n">
+        <v>42.97</v>
+      </c>
+      <c r="E7" t="n">
+        <v>85.94</v>
       </c>
     </row>
     <row r="8">
@@ -616,20 +580,14 @@
           <t>Cup - Cold (16oz)</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>84.44</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>84.44</t>
-        </is>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>84.44</v>
+      </c>
+      <c r="E8" t="n">
+        <v>84.44</v>
       </c>
     </row>
     <row r="9">
@@ -643,20 +601,14 @@
           <t>Container - Paper Clamshell (Bagel Box)</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>69.94</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>349.70</t>
-        </is>
+      <c r="C9" t="n">
+        <v>5</v>
+      </c>
+      <c r="D9" t="n">
+        <v>69.94</v>
+      </c>
+      <c r="E9" t="n">
+        <v>349.7</v>
       </c>
     </row>
     <row r="10">
@@ -670,20 +622,14 @@
           <t>Container - Paper Clamshell (Avocado Box)</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>56.85</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>56.85</t>
-        </is>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="n">
+        <v>56.85</v>
+      </c>
+      <c r="E10" t="n">
+        <v>56.85</v>
       </c>
     </row>
     <row r="11">
@@ -697,20 +643,14 @@
           <t>Cup - Cold (12oz)</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>75.32</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>75.32</t>
-        </is>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="n">
+        <v>75.31999999999999</v>
+      </c>
+      <c r="E11" t="n">
+        <v>75.31999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -724,20 +664,14 @@
           <t>Bag - Wax (6#)</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>74.23</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>74.23</t>
-        </is>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>74.23</v>
+      </c>
+      <c r="E12" t="n">
+        <v>74.23</v>
       </c>
     </row>
   </sheetData>
